--- a/data/trans_orig/P57B5_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B5_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido rebosante de energía en 2023</t>
+          <t>Población según se ha sentido rebosante de energía en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48383</t>
+          <t>52734</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>13777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54710</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184833</t>
+          <t>184784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224983</t>
+          <t>223678</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164265</t>
+          <t>162765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>192648</t>
+          <t>190872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>358711</t>
+          <t>360092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>407537</t>
+          <t>408289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58817</t>
+          <t>58062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91692</t>
+          <t>89473</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81037</t>
+          <t>83067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107270</t>
+          <t>109837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>147573</t>
+          <t>147401</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>188934</t>
+          <t>189211</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28839</t>
+          <t>29783</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>235132</t>
+          <t>233541</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>293772</t>
+          <t>294116</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177594</t>
+          <t>177493</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>216007</t>
+          <t>217876</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>426870</t>
+          <t>427435</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>500262</t>
+          <t>495693</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167876</t>
+          <t>168383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>222862</t>
+          <t>225797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207778</t>
+          <t>207253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249071</t>
+          <t>247959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>389131</t>
+          <t>392829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>458478</t>
+          <t>461109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30559</t>
+          <t>30830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58603</t>
+          <t>59936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49100</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72887</t>
+          <t>73892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86118</t>
+          <t>85999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123737</t>
+          <t>123930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27008</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20241</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37176</t>
+          <t>37241</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>31899</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56853</t>
+          <t>56504</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125331</t>
+          <t>127163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161550</t>
+          <t>161688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104000</t>
+          <t>105855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136601</t>
+          <t>135732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>241591</t>
+          <t>240701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292057</t>
+          <t>289222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80571</t>
+          <t>79934</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>112579</t>
+          <t>109698</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102986</t>
+          <t>102002</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>132847</t>
+          <t>132311</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>189683</t>
+          <t>189861</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>232929</t>
+          <t>231686</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66839</t>
+          <t>66005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59772</t>
+          <t>60857</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84912</t>
+          <t>84571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109680</t>
+          <t>110927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143847</t>
+          <t>145392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32965</t>
+          <t>32666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27615</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44186</t>
+          <t>44900</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>47221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71945</t>
+          <t>70273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>130536</t>
+          <t>127172</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175320</t>
+          <t>173803</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80330</t>
+          <t>81377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179172</t>
+          <t>180920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>211048</t>
+          <t>199019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>338660</t>
+          <t>334298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79879</t>
+          <t>79081</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117251</t>
+          <t>120445</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>172392</t>
+          <t>171011</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>331514</t>
+          <t>329372</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>268702</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>459655</t>
+          <t>461176</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,21%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>55778</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>43023</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91797</t>
+          <t>93089</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>80037</t>
+          <t>80222</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135994</t>
+          <t>133958</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32546</t>
+          <t>31891</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>36766</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31627</t>
+          <t>31798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62090</t>
+          <t>61157</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22605</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>42909</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13951</t>
+          <t>14505</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27317</t>
+          <t>27419</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40195</t>
+          <t>40451</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76800</t>
+          <t>76247</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100068</t>
+          <t>98325</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73703</t>
+          <t>74074</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93879</t>
+          <t>95104</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157405</t>
+          <t>157032</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188516</t>
+          <t>186673</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46863</t>
+          <t>46798</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66442</t>
+          <t>66391</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89350</t>
+          <t>90649</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>109962</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>142868</t>
+          <t>142848</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>171131</t>
+          <t>172124</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>477</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>108300</t>
+          <t>108113</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138526</t>
+          <t>139467</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90612</t>
+          <t>89091</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>115826</t>
+          <t>115152</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>205971</t>
+          <t>205248</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>246814</t>
+          <t>246650</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>67594</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>97644</t>
+          <t>95932</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>72146</t>
+          <t>72417</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>95595</t>
+          <t>96101</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>146218</t>
+          <t>146969</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>183832</t>
+          <t>183342</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36950</t>
+          <t>36709</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>56943</t>
+          <t>56659</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>35115</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>53736</t>
+          <t>52454</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>76344</t>
+          <t>77658</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>104940</t>
+          <t>104379</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26665</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>37262</t>
+          <t>37443</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>56158</t>
+          <t>56359</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>238126</t>
+          <t>237205</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>299350</t>
+          <t>301246</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>104950</t>
+          <t>101048</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>284722</t>
+          <t>285414</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>313595</t>
+          <t>298414</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>570259</t>
+          <t>567595</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>213193</t>
+          <t>212830</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>271599</t>
+          <t>270345</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>348193</t>
+          <t>342466</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>656822</t>
+          <t>660914</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>582126</t>
+          <t>579371</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>989786</t>
+          <t>1003896</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>68,19%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>72821</t>
+          <t>73160</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>111675</t>
+          <t>111963</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>57859</t>
+          <t>57633</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>158998</t>
+          <t>161428</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>124160</t>
+          <t>123000</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>249214</t>
+          <t>250964</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>14297</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34942</t>
+          <t>35563</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>71390</t>
+          <t>71616</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>43662</t>
+          <t>44792</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>91706</t>
+          <t>92139</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>391600</t>
+          <t>391225</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>754987</t>
+          <t>756332</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>222080</t>
+          <t>221646</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>268682</t>
+          <t>264545</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>623406</t>
+          <t>619570</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1095932</t>
+          <t>1114510</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>113351</t>
+          <t>112155</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>353991</t>
+          <t>353065</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>280915</t>
+          <t>279413</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>326687</t>
+          <t>322670</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>358545</t>
+          <t>344539</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>663170</t>
+          <t>665043</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>45945</t>
+          <t>50338</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>153920</t>
+          <t>157108</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>114887</t>
+          <t>116304</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>148359</t>
+          <t>147891</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>151616</t>
+          <t>148491</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>289026</t>
+          <t>294887</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>31104</t>
+          <t>30754</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>59989</t>
+          <t>60779</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>41350</t>
+          <t>41552</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>89785</t>
+          <t>89725</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1384710</t>
+          <t>1386095</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2007510</t>
+          <t>2037101</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>842755</t>
+          <t>840669</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1123970</t>
+          <t>1128748</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,17 +5347,17 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2586330</t>
+          <t>2586331</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2348496</t>
+          <t>2339581</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3114033</t>
+          <t>3132339</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>963695</t>
+          <t>946436</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1375661</t>
+          <t>1380549</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1547874</t>
+          <t>1542845</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2105454</t>
+          <t>2069430</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2682597</t>
+          <t>2662257</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3351969</t>
+          <t>3330640</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>387416</t>
+          <t>383747</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>571091</t>
+          <t>564978</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>551040</t>
+          <t>567094</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>749648</t>
+          <t>756029</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1042357</t>
+          <t>1044341</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1300598</t>
+          <t>1297988</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>103210</t>
+          <t>101090</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>161817</t>
+          <t>157080</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>181624</t>
+          <t>185491</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>256074</t>
+          <t>259761</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>312689</t>
+          <t>310195</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>403442</t>
+          <t>400583</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7102823</t>
+          <t>7102824</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7102823</t>
+          <t>7102824</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7102823</t>
+          <t>7102824</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">

--- a/data/trans_orig/P57B5_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B5_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52734</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>554</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50866</t>
+          <t>31948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>206646</t>
+          <t>213293</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184784</t>
+          <t>196149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>223678</t>
+          <t>229982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>178633</t>
+          <t>191534</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162765</t>
+          <t>177832</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>190872</t>
+          <t>205579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>385278</t>
+          <t>404827</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>360092</t>
+          <t>383812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>408289</t>
+          <t>428384</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73297</t>
+          <t>80517</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58062</t>
+          <t>65725</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89473</t>
+          <t>95590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94275</t>
+          <t>106723</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83067</t>
+          <t>93585</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109837</t>
+          <t>120706</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>167572</t>
+          <t>187240</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>147401</t>
+          <t>166026</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>189211</t>
+          <t>206524</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>10903</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>17250</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>16753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29783</t>
+          <t>30888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>264268</t>
+          <t>267364</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>233541</t>
+          <t>238301</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>294116</t>
+          <t>294682</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>196692</t>
+          <t>208855</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177493</t>
+          <t>189210</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>217876</t>
+          <t>229060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>460960</t>
+          <t>476219</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>427435</t>
+          <t>442870</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>495693</t>
+          <t>515041</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>196628</t>
+          <t>203635</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168383</t>
+          <t>175421</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>225797</t>
+          <t>230253</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>227653</t>
+          <t>242539</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207253</t>
+          <t>222873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>247959</t>
+          <t>264234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>424280</t>
+          <t>446174</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>392829</t>
+          <t>408165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>461109</t>
+          <t>479965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42591</t>
+          <t>44495</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30830</t>
+          <t>32426</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59936</t>
+          <t>62192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61090</t>
+          <t>64454</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49378</t>
+          <t>52135</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73892</t>
+          <t>77010</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>103681</t>
+          <t>108949</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85999</t>
+          <t>90585</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123930</t>
+          <t>129245</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27746</t>
+          <t>27201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>28867</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37241</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>42779</t>
+          <t>44020</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31899</t>
+          <t>33369</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>59350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>513311</t>
+          <t>544715</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>513311</t>
+          <t>544715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>513311</t>
+          <t>544715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1031701</t>
+          <t>1075362</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1031701</t>
+          <t>1075362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1031701</t>
+          <t>1075362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>143587</t>
+          <t>143045</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127163</t>
+          <t>123804</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161688</t>
+          <t>159227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>121195</t>
+          <t>123988</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105855</t>
+          <t>107766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135732</t>
+          <t>139584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>264782</t>
+          <t>267032</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240701</t>
+          <t>243991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>289222</t>
+          <t>291355</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94447</t>
+          <t>95133</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79934</t>
+          <t>81327</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>109698</t>
+          <t>110950</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>116496</t>
+          <t>121800</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102002</t>
+          <t>106497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>132311</t>
+          <t>137691</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>210943</t>
+          <t>216933</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>189861</t>
+          <t>197053</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>231686</t>
+          <t>238462</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>53910</t>
+          <t>52574</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42599</t>
+          <t>40783</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66005</t>
+          <t>66191</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>72563</t>
+          <t>73036</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60857</t>
+          <t>61419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84571</t>
+          <t>86146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>126473</t>
+          <t>125610</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110927</t>
+          <t>109515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145392</t>
+          <t>144028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23475</t>
+          <t>24633</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32666</t>
+          <t>35392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34951</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>27908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44900</t>
+          <t>45149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>58426</t>
+          <t>60410</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47221</t>
+          <t>49221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70273</t>
+          <t>74611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>345205</t>
+          <t>354601</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>345205</t>
+          <t>354601</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>345205</t>
+          <t>354601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>660623</t>
+          <t>669985</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>660623</t>
+          <t>669985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>660623</t>
+          <t>669985</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>150377</t>
+          <t>190773</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>127172</t>
+          <t>165863</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173803</t>
+          <t>215577</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>141017</t>
+          <t>165218</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81377</t>
+          <t>144344</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180920</t>
+          <t>184123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>291394</t>
+          <t>355991</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>199019</t>
+          <t>323077</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>334298</t>
+          <t>391373</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>98909</t>
+          <t>113014</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79081</t>
+          <t>91793</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120445</t>
+          <t>134187</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>232524</t>
+          <t>146489</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>171011</t>
+          <t>129647</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329372</t>
+          <t>164214</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>331433</t>
+          <t>259502</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>229754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>461176</t>
+          <t>291628</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39022</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27982</t>
+          <t>29613</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55778</t>
+          <t>57312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71089</t>
+          <t>77307</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43023</t>
+          <t>63146</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93089</t>
+          <t>89965</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>110111</t>
+          <t>119593</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>80222</t>
+          <t>100130</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>133958</t>
+          <t>143610</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19913</t>
+          <t>22388</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31891</t>
+          <t>37005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26037</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15284</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36766</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45950</t>
+          <t>50031</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31798</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61157</t>
+          <t>67760</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>308220</t>
+          <t>368461</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>308220</t>
+          <t>368461</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>308220</t>
+          <t>368461</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>470668</t>
+          <t>416657</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>470668</t>
+          <t>416657</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>470668</t>
+          <t>416657</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>778888</t>
+          <t>785118</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>778888</t>
+          <t>785118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>778888</t>
+          <t>785118</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31181</t>
+          <t>37395</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>26884</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42909</t>
+          <t>50314</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>16731</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>32269</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>51304</t>
+          <t>60058</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40451</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64932</t>
+          <t>75780</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>88215</t>
+          <t>100973</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76247</t>
+          <t>86258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98325</t>
+          <t>114098</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>84245</t>
+          <t>93626</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74074</t>
+          <t>82697</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95104</t>
+          <t>104323</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>172460</t>
+          <t>194599</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157032</t>
+          <t>177630</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>186673</t>
+          <t>210043</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>56500</t>
+          <t>64196</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46798</t>
+          <t>53162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66391</t>
+          <t>74882</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100151</t>
+          <t>106309</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>90649</t>
+          <t>96194</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>117219</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>156651</t>
+          <t>170505</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>142848</t>
+          <t>154863</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>172124</t>
+          <t>186209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>43,24%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>519</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>177667</t>
+          <t>204554</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>177667</t>
+          <t>204554</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>177667</t>
+          <t>204554</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>207537</t>
+          <t>226048</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207537</t>
+          <t>226048</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207537</t>
+          <t>226048</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>385204</t>
+          <t>430602</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>385204</t>
+          <t>430602</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>385204</t>
+          <t>430602</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>123127</t>
+          <t>120829</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>108113</t>
+          <t>106068</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>139467</t>
+          <t>136865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>103487</t>
+          <t>104889</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>89091</t>
+          <t>92178</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>115152</t>
+          <t>118517</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>226614</t>
+          <t>225718</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>205248</t>
+          <t>204686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>246650</t>
+          <t>244561</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>81736</t>
+          <t>85122</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>67594</t>
+          <t>72324</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>95932</t>
+          <t>98541</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>82942</t>
+          <t>86065</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>72417</t>
+          <t>74821</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>96101</t>
+          <t>99394</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>164678</t>
+          <t>171187</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>146969</t>
+          <t>152596</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>183342</t>
+          <t>188871</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>46563</t>
+          <t>47100</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36709</t>
+          <t>37582</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>56659</t>
+          <t>57908</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>44813</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35115</t>
+          <t>35932</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52454</t>
+          <t>55804</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>91914</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>77658</t>
+          <t>79420</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>104379</t>
+          <t>107762</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12308</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>26013</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>27540</t>
+          <t>27983</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>21722</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>35421</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>45750</t>
+          <t>45638</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>36706</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>56359</t>
+          <t>55665</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>269187</t>
+          <t>303302</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>237205</t>
+          <t>274385</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>301246</t>
+          <t>337145</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>209551</t>
+          <t>250835</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>101048</t>
+          <t>224889</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>285414</t>
+          <t>277001</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>478737</t>
+          <t>554137</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>298414</t>
+          <t>515048</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>567595</t>
+          <t>596331</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>40,02%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>241162</t>
+          <t>290385</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>212830</t>
+          <t>261163</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>270345</t>
+          <t>318908</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>474160</t>
+          <t>324447</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>342466</t>
+          <t>297896</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>660914</t>
+          <t>349435</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>715321</t>
+          <t>614833</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>579371</t>
+          <t>578925</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1003896</t>
+          <t>653842</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>90123</t>
+          <t>100033</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>73160</t>
+          <t>82342</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>111963</t>
+          <t>123141</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>115890</t>
+          <t>137247</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>57633</t>
+          <t>118574</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>161428</t>
+          <t>157813</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>206012</t>
+          <t>237280</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>123000</t>
+          <t>209826</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>250964</t>
+          <t>272770</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>25169</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>15935</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>37208</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>49020</t>
+          <t>58837</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>45805</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>71616</t>
+          <t>73206</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>72116</t>
+          <t>84006</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>44792</t>
+          <t>68284</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>92139</t>
+          <t>100941</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>623567</t>
+          <t>718890</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>623567</t>
+          <t>718890</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623567</t>
+          <t>718890</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>848620</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>848620</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>848620</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1472187</t>
+          <t>1490257</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1472187</t>
+          <t>1490257</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1472187</t>
+          <t>1490257</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>542659</t>
+          <t>357719</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>391225</t>
+          <t>330192</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>756332</t>
+          <t>388147</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>243510</t>
+          <t>283411</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>221646</t>
+          <t>257143</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>264545</t>
+          <t>309531</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>786170</t>
+          <t>641130</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>619570</t>
+          <t>601868</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1114510</t>
+          <t>681371</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>251972</t>
+          <t>289482</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>112155</t>
+          <t>259643</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>353065</t>
+          <t>319916</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>302016</t>
+          <t>352079</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>279413</t>
+          <t>328792</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>322670</t>
+          <t>378473</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>553988</t>
+          <t>641561</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>344539</t>
+          <t>602657</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>665043</t>
+          <t>681678</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>108095</t>
+          <t>120207</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>101014</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>157108</t>
+          <t>140453</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>131235</t>
+          <t>154050</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>116304</t>
+          <t>134527</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>147891</t>
+          <t>174207</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>239331</t>
+          <t>274257</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>148491</t>
+          <t>248081</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>294887</t>
+          <t>304470</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>30664</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>41262</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>40970</t>
+          <t>41791</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>30754</t>
+          <t>31574</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>60779</t>
+          <t>53520</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>66963</t>
+          <t>72455</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>41552</t>
+          <t>58425</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>89725</t>
+          <t>88045</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1550589</t>
+          <t>1439562</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1386095</t>
+          <t>1368687</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2037101</t>
+          <t>1506083</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1035742</t>
+          <t>1160413</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>840669</t>
+          <t>1103036</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1128748</t>
+          <t>1211450</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2586331</t>
+          <t>2599975</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2339581</t>
+          <t>2511928</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3132339</t>
+          <t>2687293</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1259715</t>
+          <t>1391037</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>946436</t>
+          <t>1326609</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1380549</t>
+          <t>1456064</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1698668</t>
+          <t>1558579</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1542845</t>
+          <t>1503497</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2069430</t>
+          <t>1613350</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2958382</t>
+          <t>2949616</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2662257</t>
+          <t>2865490</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3330640</t>
+          <t>3033907</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>510100</t>
+          <t>551409</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>383747</t>
+          <t>508398</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>564978</t>
+          <t>597123</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>689381</t>
+          <t>763939</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>567094</t>
+          <t>722522</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>756029</t>
+          <t>804719</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1199481</t>
+          <t>1315348</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1044341</t>
+          <t>1253253</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1297988</t>
+          <t>1380159</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>132658</t>
+          <t>143552</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>101090</t>
+          <t>123417</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>157080</t>
+          <t>168869</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>225973</t>
+          <t>241598</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>185491</t>
+          <t>218882</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>259761</t>
+          <t>267511</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>358630</t>
+          <t>385151</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>310195</t>
+          <t>350008</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>400583</t>
+          <t>419181</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3453061</t>
+          <t>3525560</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3453061</t>
+          <t>3525560</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3453061</t>
+          <t>3525560</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3649763</t>
+          <t>3724529</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3649763</t>
+          <t>3724529</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3649763</t>
+          <t>3724529</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7102824</t>
+          <t>7250090</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7102824</t>
+          <t>7250090</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7102824</t>
+          <t>7250090</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
